--- a/tools/importer/reports/import-landing-page.report.xlsx
+++ b/tools/importer/reports/import-landing-page.report.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="98">
   <si>
     <t>_reportFile</t>
   </si>
@@ -37,6 +37,87 @@
     <t>url</t>
   </si>
   <si>
+    <t>blog.report.json</t>
+  </si>
+  <si>
+    <t>["hero-minimal-light-withimg-1","hero-minimal-dark-withimg","cards-minimal-light-withimg-1"]</t>
+  </si>
+  <si>
+    <t>blog</t>
+  </si>
+  <si>
+    <t>success</t>
+  </si>
+  <si>
+    <t>listing-page</t>
+  </si>
+  <si>
+    <t>2026-09-03T10:06:16.057Z</t>
+  </si>
+  <si>
+    <t>Blog — WKND Trendsetters</t>
+  </si>
+  <si>
+    <t>https://wknd-trendsetters.site/blog</t>
+  </si>
+  <si>
+    <t>case-studies.report.json</t>
+  </si>
+  <si>
+    <t>["hero-minimal-light-withimg-1","hero-minimal-dark-withimg","cards-minimal-light-withimg","tabs-minimal-light-withimg","banner-minimal-dark-withimg"]</t>
+  </si>
+  <si>
+    <t>case-studies</t>
+  </si>
+  <si>
+    <t>2026-09-03T10:06:20.919Z</t>
+  </si>
+  <si>
+    <t>Inspiring Case Studies | Fashion Blog</t>
+  </si>
+  <si>
+    <t>https://wknd-trendsetters.site/case-studies</t>
+  </si>
+  <si>
+    <t>faq.report.json</t>
+  </si>
+  <si>
+    <t>["hero-minimal-light-withimg-1","accordion-moderate-light","columns-minimal-light"]</t>
+  </si>
+  <si>
+    <t>faq</t>
+  </si>
+  <si>
+    <t>faq-accordion</t>
+  </si>
+  <si>
+    <t>2026-09-03T10:20:21.168Z</t>
+  </si>
+  <si>
+    <t>FAQ - The Fashion Blog</t>
+  </si>
+  <si>
+    <t>https://wknd-trendsetters.site/faq</t>
+  </si>
+  <si>
+    <t>fashion-insights.report.json</t>
+  </si>
+  <si>
+    <t>["hero-minimal-light-withimg-1","hero-minimal-dark-withimg","cards-minimal-light-withimg-1","cards-minimal-light-withimg"]</t>
+  </si>
+  <si>
+    <t>fashion-insights</t>
+  </si>
+  <si>
+    <t>2026-09-03T10:06:25.030Z</t>
+  </si>
+  <si>
+    <t>Fashion Blog - Discover Trends in Young Fashion</t>
+  </si>
+  <si>
+    <t>https://wknd-trendsetters.site/fashion-insights</t>
+  </si>
+  <si>
     <t>fashion-trends-of-the-season.report.json</t>
   </si>
   <si>
@@ -46,13 +127,10 @@
     <t>fashion-trends-of-the-season</t>
   </si>
   <si>
-    <t>success</t>
-  </si>
-  <si>
     <t>landing-page</t>
   </si>
   <si>
-    <t>2026-09-03T09:43:07.133Z</t>
+    <t>2026-09-03T10:52:58.133Z</t>
   </si>
   <si>
     <t>Top Fashion Trends for Young People | Fashion Blog</t>
@@ -61,6 +139,27 @@
     <t>https://wknd-trendsetters.site/fashion-trends-of-the-season</t>
   </si>
   <si>
+    <t>fashion-trends-young-adults-casual-sport.report.json</t>
+  </si>
+  <si>
+    <t>["hero-minimal-light-withimg-1","cards-minimal-light-withimg-1","columns-minimal-light-withimg"]</t>
+  </si>
+  <si>
+    <t>fashion-trends-young-adults-casual-sport</t>
+  </si>
+  <si>
+    <t>content-detail</t>
+  </si>
+  <si>
+    <t>2026-09-03T10:52:34.672Z</t>
+  </si>
+  <si>
+    <t>Fashion Trends for Young Adults | Fashion Blog</t>
+  </si>
+  <si>
+    <t>https://wknd-trendsetters.site/fashion-trends-young-adults-casual-sport</t>
+  </si>
+  <si>
     <t>fashion-trends-young-adults.report.json</t>
   </si>
   <si>
@@ -70,7 +169,7 @@
     <t>fashion-trends-young-adults</t>
   </si>
   <si>
-    <t>2026-09-03T09:43:11.626Z</t>
+    <t>2026-09-03T10:53:01.816Z</t>
   </si>
   <si>
     <t>Fashion Trends for Young Adults - Fashion Blog</t>
@@ -88,7 +187,7 @@
     <t>index</t>
   </si>
   <si>
-    <t>2026-09-03T09:40:03.051Z</t>
+    <t>2026-09-03T10:52:53.485Z</t>
   </si>
   <si>
     <t>WKND Trendsetters - Fresh Looks, Bold Stories, Real Life</t>
@@ -594,11 +693,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H11"/>
+  <dimension ref="A1:H16"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="2" width="50" customWidth="1"/>
-    <col min="3" max="3" width="41" customWidth="1"/>
+    <col min="3" max="3" width="42" customWidth="1"/>
     <col min="5" max="5" width="16" customWidth="1"/>
     <col min="6" max="6" width="26" customWidth="1"/>
     <col min="7" max="8" width="50" customWidth="1"/>
@@ -696,33 +795,33 @@
         <v>11</v>
       </c>
       <c r="E4" t="s">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="F4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G4" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="H4" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B5" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C5" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D5" t="s">
         <v>11</v>
       </c>
       <c r="E5" t="s">
-        <v>31</v>
+        <v>12</v>
       </c>
       <c r="F5" t="s">
         <v>32</v>
@@ -739,155 +838,285 @@
         <v>35</v>
       </c>
       <c r="B6" t="s">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="C6" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D6" t="s">
         <v>11</v>
       </c>
       <c r="E6" t="s">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="F6" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="G6" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="H6" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B7" t="s">
-        <v>29</v>
+        <v>43</v>
       </c>
       <c r="C7" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="D7" t="s">
         <v>11</v>
       </c>
       <c r="E7" t="s">
-        <v>31</v>
+        <v>45</v>
       </c>
       <c r="F7" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="G7" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="H7" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="B8" t="s">
-        <v>29</v>
+        <v>50</v>
       </c>
       <c r="C8" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="D8" t="s">
         <v>11</v>
       </c>
       <c r="E8" t="s">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="F8" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="G8" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="H8" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="B9" t="s">
-        <v>29</v>
+        <v>56</v>
       </c>
       <c r="C9" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="D9" t="s">
         <v>11</v>
       </c>
       <c r="E9" t="s">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="F9" t="s">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="G9" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="H9" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="B10" t="s">
-        <v>29</v>
+        <v>62</v>
       </c>
       <c r="C10" t="s">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="D10" t="s">
         <v>11</v>
       </c>
       <c r="E10" t="s">
-        <v>31</v>
+        <v>64</v>
       </c>
       <c r="F10" t="s">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="G10" t="s">
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="H10" t="s">
-        <v>59</v>
+        <v>67</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="B11" t="s">
-        <v>29</v>
+        <v>62</v>
       </c>
       <c r="C11" t="s">
-        <v>61</v>
+        <v>69</v>
       </c>
       <c r="D11" t="s">
         <v>11</v>
       </c>
       <c r="E11" t="s">
-        <v>31</v>
+        <v>64</v>
       </c>
       <c r="F11" t="s">
+        <v>70</v>
+      </c>
+      <c r="G11" t="s">
+        <v>71</v>
+      </c>
+      <c r="H11" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>73</v>
+      </c>
+      <c r="B12" t="s">
         <v>62</v>
       </c>
-      <c r="G11" t="s">
-        <v>63</v>
-      </c>
-      <c r="H11" t="s">
+      <c r="C12" t="s">
+        <v>74</v>
+      </c>
+      <c r="D12" t="s">
+        <v>11</v>
+      </c>
+      <c r="E12" t="s">
         <v>64</v>
+      </c>
+      <c r="F12" t="s">
+        <v>75</v>
+      </c>
+      <c r="G12" t="s">
+        <v>76</v>
+      </c>
+      <c r="H12" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>78</v>
+      </c>
+      <c r="B13" t="s">
+        <v>62</v>
+      </c>
+      <c r="C13" t="s">
+        <v>79</v>
+      </c>
+      <c r="D13" t="s">
+        <v>11</v>
+      </c>
+      <c r="E13" t="s">
+        <v>64</v>
+      </c>
+      <c r="F13" t="s">
+        <v>80</v>
+      </c>
+      <c r="G13" t="s">
+        <v>81</v>
+      </c>
+      <c r="H13" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>83</v>
+      </c>
+      <c r="B14" t="s">
+        <v>62</v>
+      </c>
+      <c r="C14" t="s">
+        <v>84</v>
+      </c>
+      <c r="D14" t="s">
+        <v>11</v>
+      </c>
+      <c r="E14" t="s">
+        <v>64</v>
+      </c>
+      <c r="F14" t="s">
+        <v>85</v>
+      </c>
+      <c r="G14" t="s">
+        <v>86</v>
+      </c>
+      <c r="H14" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>88</v>
+      </c>
+      <c r="B15" t="s">
+        <v>62</v>
+      </c>
+      <c r="C15" t="s">
+        <v>89</v>
+      </c>
+      <c r="D15" t="s">
+        <v>11</v>
+      </c>
+      <c r="E15" t="s">
+        <v>64</v>
+      </c>
+      <c r="F15" t="s">
+        <v>90</v>
+      </c>
+      <c r="G15" t="s">
+        <v>91</v>
+      </c>
+      <c r="H15" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>93</v>
+      </c>
+      <c r="B16" t="s">
+        <v>62</v>
+      </c>
+      <c r="C16" t="s">
+        <v>94</v>
+      </c>
+      <c r="D16" t="s">
+        <v>11</v>
+      </c>
+      <c r="E16" t="s">
+        <v>64</v>
+      </c>
+      <c r="F16" t="s">
+        <v>95</v>
+      </c>
+      <c r="G16" t="s">
+        <v>96</v>
+      </c>
+      <c r="H16" t="s">
+        <v>97</v>
       </c>
     </row>
   </sheetData>
